--- a/yellow-server/data/uploads/简要案情1.xlsx
+++ b/yellow-server/data/uploads/简要案情1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workprogram\扫黄\扫黄\代码\antiporn\上传模板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ADD9878-AD29-4A23-B48B-7F17593B51CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB04DAF3-694A-4442-8AD3-2310D2AEC77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="300" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -238,9 +238,6 @@
     <t>小胡</t>
   </si>
   <si>
-    <t>2025年5月14日，我所民警接线索举报称上海市松江区某地有卖淫嫖娼的情况，遂至上址检查，并经出示证件将相关人员传唤至所作进一步调查。</t>
-  </si>
-  <si>
     <t>310227199002301007</t>
   </si>
   <si>
@@ -317,10 +314,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>310227199002301000</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>近期，我局接线索掌握，在上海市松江区泗泾镇有相关卖淫嫖娼的情况。根据该线索，民警遂开展进一步调查工作。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -329,23 +322,31 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2025年5月8日，我所民警在侦办案件中，通过深挖线索发现小李等人有卖淫嫖娼的行为。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>2025年5月13日，经群众匿名举报，在上海市松江区一二三路111弄-1号商务中心11楼1101室内，有卖淫嫖娼活动。已接报</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2025年5月22日，根据警企协作获得线索，发现上海市松江区车墩镇张三等人卖淫嫖娼的违法行为，后续进一步开展侦办。</t>
+    <t>310227199002301010</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2025年5月8日，我所民警在侦办案件中，通过深挖线索发现小王等人有卖淫嫖娼的行为。</t>
+    <t>根据分局治安支队下发线索，松江区西山路81弄某SPA内有涉黄情况。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>根据分局治安支队下发线索，松江区某SPA内有涉黄情况。</t>
+    <t>2025年5月8日，我所民警在侦办案件中，通过深挖线索发现松江区迪萨社区小王等人有卖淫嫖娼的行为。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025年5月8日，我所民警在侦办案件中，通过深挖线索发现松江区桃园路90号小李等人有卖淫嫖娼的行为。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025年5月14日，我所民警接线索举报称上海市松江区桃园路90号有卖淫嫖娼的情况，遂至上址检查，并经出示证件将相关人员传唤至所作进一步调查。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025年5月22日，根据警企协作获得线索，发现上海市松江区车墩镇恒大名都小区张三等人卖淫嫖娼的违法行为，后续进一步开展侦办。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -771,7 +772,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
@@ -795,10 +796,10 @@
         <v>14</v>
       </c>
       <c r="Q1" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="R1" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>15</v>
@@ -831,7 +832,7 @@
         <v>23</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>24</v>
@@ -902,7 +903,7 @@
         <v>39</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>24</v>
@@ -973,7 +974,7 @@
         <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>24</v>
@@ -1044,7 +1045,7 @@
         <v>53</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>24</v>
@@ -1115,7 +1116,7 @@
         <v>59</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>24</v>
@@ -1186,7 +1187,7 @@
         <v>65</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>24</v>
@@ -1257,13 +1258,13 @@
         <v>71</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H8" s="1">
         <v>18</v>
@@ -1281,7 +1282,7 @@
         <v>28</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>30</v>
@@ -1305,10 +1306,10 @@
         <v>34</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="W8" s="1" t="s">
         <v>36</v>
@@ -1316,25 +1317,25 @@
     </row>
     <row r="9" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H9" s="1">
         <v>18</v>
@@ -1352,7 +1353,7 @@
         <v>28</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>30</v>
@@ -1376,10 +1377,10 @@
         <v>34</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="W9" s="1" t="s">
         <v>36</v>
@@ -1387,25 +1388,25 @@
     </row>
     <row r="10" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H10" s="1">
         <v>18</v>
@@ -1423,7 +1424,7 @@
         <v>28</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>30</v>
@@ -1447,10 +1448,10 @@
         <v>34</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="W10" s="1" t="s">
         <v>36</v>
@@ -1458,25 +1459,25 @@
     </row>
     <row r="11" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H11" s="1">
         <v>18</v>
@@ -1494,7 +1495,7 @@
         <v>28</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>30</v>
@@ -1518,10 +1519,10 @@
         <v>34</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>36</v>
